--- a/AAII_Financials/Yearly/ITT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ITT_YR_FIN.xlsx
@@ -1128,7 +1128,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>3220500</v>
+        <v>3218300</v>
       </c>
       <c r="E17" s="3">
         <v>2992500</v>
@@ -1179,7 +1179,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>718000</v>
+        <v>720200</v>
       </c>
       <c r="E18" s="3">
         <v>638200</v>
@@ -1251,7 +1251,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-5500</v>
+        <v>-3300</v>
       </c>
       <c r="E20" s="3">
         <v>-1800</v>
@@ -1863,7 +1863,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="E32" s="3">
         <v>1800</v>
